--- a/config/Telemetry_Catalog_v3.15.1.xlsx
+++ b/config/Telemetry_Catalog_v3.15.1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hasidhu/Downloads/nvdebug/2.0/debug_builds/final_build/nvdebug/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hasidhu/Downloads/nvdebug/2.0/github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725744B3-8663-5146-B598-C3C29C3001F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BF6A8C-0749-FA45-91A8-E8FA2BA3F5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
